--- a/backend/data/financials_by_company/1AI.AX.xlsx
+++ b/backend/data/financials_by_company/1AI.AX.xlsx
@@ -2968,10 +2968,8 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
+      <c r="E2" t="n">
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3181,7 +3179,7 @@
         <v>-1014154</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>1.2</v>
@@ -3350,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.0014599999</v>
